--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486679_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486679_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9029</v>
+        <v>2.8202</v>
       </c>
       <c r="E2" t="n">
-        <v>5.4354</v>
+        <v>5.2285</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.5325</v>
+        <v>-2.4083</v>
       </c>
       <c r="G2" t="n">
         <v>1.7623</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4966</v>
+        <v>-0.5793</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0547</v>
+        <v>-0.1521</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5513</v>
+        <v>-0.4271</v>
       </c>
       <c r="V2" t="n">
         <v>0.2856</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. MARTINEZ MESEGUER</t>
+          <t>A. ROMERO GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9865</v>
+        <v>1.6248</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4</v>
+        <v>1.9979</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4135</v>
+        <v>-0.3732</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2291</v>
+        <v>1.0111</v>
       </c>
       <c r="H3" t="n">
-        <v>-3.6004</v>
+        <v>-0.6211</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8295</v>
+        <v>1.6322</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2098</v>
+        <v>2.1705</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.0479</v>
+        <v>0.8277</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2577</v>
+        <v>1.3428</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9807</v>
+        <v>-1.1594</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.5526</v>
+        <v>-1.4488</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5719</v>
+        <v>0.2893</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6841</v>
+        <v>-0.1586</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2754</v>
+        <v>-0.1726</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4087</v>
+        <v>0.014</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0852</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0852</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ROMERO GARCIA</t>
+          <t>I. MARTINEZ MESEGUER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2979</v>
+        <v>1.4816</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8945</v>
+        <v>2.1931</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5966</v>
+        <v>-0.7115</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0111</v>
+        <v>0.2291</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6211</v>
+        <v>-3.6004</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6322</v>
+        <v>3.8295</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1705</v>
+        <v>2.2098</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8277</v>
+        <v>-1.0479</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3428</v>
+        <v>3.2577</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1594</v>
+        <v>-1.9807</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4488</v>
+        <v>-2.5526</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2893</v>
+        <v>0.5719</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.4855</v>
+        <v>0.1793</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.276</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2095</v>
+        <v>0.1107</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.0852</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-0.0852</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0422</v>
+        <v>-0.2987</v>
       </c>
       <c r="E5" t="n">
-        <v>3.8961</v>
+        <v>3.6892</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.9382</v>
+        <v>-3.9879</v>
       </c>
       <c r="G5" t="n">
         <v>1.3327</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1158</v>
+        <v>-0.3723</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0547</v>
+        <v>-0.1521</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1705</v>
+        <v>-0.2202</v>
       </c>
       <c r="V5" t="n">
         <v>0.2856</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.327</v>
+        <v>-0.7932</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8662</v>
+        <v>2.1764</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1932</v>
+        <v>-2.9697</v>
       </c>
       <c r="G6" t="n">
         <v>2.5413</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0647</v>
+        <v>-0.5309</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5795</v>
+        <v>-0.2692</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4852</v>
+        <v>-0.2617</v>
       </c>
       <c r="V6" t="n">
         <v>0.2856</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4083</v>
+        <v>-1.3586</v>
       </c>
       <c r="E7" t="n">
         <v>-0.6826</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7257</v>
+        <v>-0.676</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3862</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0221</v>
+        <v>0.0276</v>
       </c>
       <c r="T7" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2484</v>
+        <v>-4.2981</v>
       </c>
       <c r="E8" t="n">
         <v>-1.4011</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.8473</v>
+        <v>-2.897</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0639</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2537</v>
+        <v>-0.3034</v>
       </c>
       <c r="T8" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0222</v>
+        <v>-0.0275</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5312</v>
+        <v>-4.4486</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.9207</v>
+        <v>-2.7139</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6105</v>
+        <v>-1.7347</v>
       </c>
       <c r="G9" t="n">
         <v>-3.9975</v>
@@ -1156,13 +1156,13 @@
         <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6342</v>
+        <v>-0.5516</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>-0.345</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0824</v>
+        <v>-0.2066</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2856</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.8577</v>
+        <v>-7.9571</v>
       </c>
       <c r="E10" t="n">
         <v>-3.7891</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0686</v>
+        <v>-4.168</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6027</v>
@@ -1234,13 +1234,13 @@
         <v>0.9654</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2318</v>
+        <v>-0.3311</v>
       </c>
       <c r="T10" t="n">
         <v>-0.3037</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07190000000000001</v>
+        <v>-0.0274</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1271</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.2275</v>
+        <v>-13.2277</v>
       </c>
       <c r="E11" t="n">
-        <v>6.698700000000002</v>
+        <v>6.698399999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.9261</v>
+        <v>-19.9263</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1738</v>
@@ -1303,7 +1303,7 @@
         <v>-2.5211</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.7923</v>
+        <v>-5.792299999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-12.5502</v>
@@ -1312,10 +1312,10 @@
         <v>6.7577</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.620299999999999</v>
+        <v>-2.6203</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.6573</v>
+        <v>-1.6572</v>
       </c>
       <c r="U11" t="n">
         <v>-0.963</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.1868</v>
+        <v>9.312099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>9.485900000000001</v>
+        <v>9.796200000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2991</v>
+        <v>-0.484</v>
       </c>
       <c r="G12" t="n">
         <v>6.7753</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8056</v>
+        <v>0.9308999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.2272</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8887</v>
+        <v>0.7037</v>
       </c>
       <c r="V12" t="n">
         <v>1.7989</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.525</v>
+        <v>4.0561</v>
       </c>
       <c r="E13" t="n">
-        <v>6.4667</v>
+        <v>5.8462</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9417</v>
+        <v>-1.79</v>
       </c>
       <c r="G13" t="n">
         <v>3.3212</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>1.1032</v>
+        <v>0.6343</v>
       </c>
       <c r="T13" t="n">
-        <v>0.772</v>
+        <v>0.1514</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3313</v>
+        <v>0.4829</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2856</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. LUIS HERRERA</t>
+          <t>M. SOSA FRANCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.36</v>
+        <v>2.8152</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5528</v>
+        <v>3.2739</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1927</v>
+        <v>-0.4588</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9317</v>
+        <v>0.9631</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2287</v>
+        <v>0.4069</v>
       </c>
       <c r="I14" t="n">
-        <v>0.703</v>
+        <v>0.5562</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2844</v>
+        <v>2.6672</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4706</v>
+        <v>1.4418</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8138</v>
+        <v>1.2253</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3527</v>
+        <v>-1.7041</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2418</v>
+        <v>-1.0349</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1108</v>
+        <v>-0.6692</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4549</v>
+        <v>0.3654</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4614</v>
+        <v>-0.0071</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9935</v>
+        <v>0.3725</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7989</v>
+        <v>0.3282</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.7989</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SOSA FRANCO</t>
+          <t>N. LUIS HERRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.6262</v>
+        <v>2.2981</v>
       </c>
       <c r="E15" t="n">
-        <v>3.5842</v>
+        <v>3.7254</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.958</v>
+        <v>-1.4273</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9631</v>
+        <v>1.9317</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4069</v>
+        <v>1.2287</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5562</v>
+        <v>0.703</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6672</v>
+        <v>3.2844</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4418</v>
+        <v>2.4706</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2253</v>
+        <v>0.8138</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7041</v>
+        <v>-1.3527</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0349</v>
+        <v>-1.2418</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.6692</v>
+        <v>-0.1108</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1764</v>
+        <v>1.3929</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3032</v>
+        <v>0.6341</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1268</v>
+        <v>0.7589</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3282</v>
+        <v>-1.7989</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2856</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.142</v>
+        <v>1.9048</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8806</v>
+        <v>1.4669</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2614</v>
+        <v>0.4379</v>
       </c>
       <c r="G16" t="n">
         <v>0.5906</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4855</v>
+        <v>0.2483</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4136</v>
+        <v>-0.0001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.2484</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2856</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7214</v>
+        <v>1.3282</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0214</v>
+        <v>1.4214</v>
       </c>
       <c r="G17" t="n">
         <v>-1.6592</v>
@@ -1780,13 +1780,13 @@
         <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4689</v>
+        <v>0.1379</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.193</v>
+        <v>0.2069</v>
       </c>
       <c r="V17" t="n">
         <v>1.8842</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1545</v>
+        <v>0.1793</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1545</v>
+        <v>0.1793</v>
       </c>
       <c r="G18" t="n">
         <v>0.1379</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0166</v>
+        <v>0.0414</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SOW SOW</t>
+          <t>A. NAVAS CERVERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8759</v>
+        <v>-0.3045</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0552</v>
+        <v>0.8141</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8208</v>
+        <v>-1.1186</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2069</v>
+        <v>-3.169</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2069</v>
+        <v>-1.6341</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-1.535</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.5013</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5735</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.0722</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2069</v>
+        <v>-3.6703</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2069</v>
+        <v>-2.2076</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-1.4627</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.9308</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0552</v>
+        <v>0.6481</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0552</v>
+        <v>0.2203</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.4278</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6138</v>
+        <v>0.2856</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. NAVAS CERVERA</t>
+          <t>M. SOW SOW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0299</v>
+        <v>-0.8759</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4004</v>
+        <v>-0.0552</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4303</v>
+        <v>-0.8208</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.169</v>
+        <v>-0.2069</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6341</v>
+        <v>-0.2069</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.535</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5013</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5735</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0722</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.6703</v>
+        <v>-0.2069</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2076</v>
+        <v>-0.2069</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4627</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9308</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1239</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.0552</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1934</v>
+        <v>-0.0552</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1161</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2856</v>
+        <v>-0.6138</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2472</v>
+        <v>-1.7371</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9024</v>
+        <v>-2.1784</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3448</v>
+        <v>0.4414</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0887</v>
@@ -2092,13 +2092,13 @@
         <v>1.7377</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3516</v>
+        <v>0.1585</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7725</v>
+        <v>-0.0486</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.2071</v>
       </c>
       <c r="V21" t="n">
         <v>0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3351</v>
+        <v>-3.6801</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1867</v>
+        <v>-2.6696</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1485</v>
+        <v>-1.0106</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4222</v>
@@ -2170,13 +2170,13 @@
         <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4689</v>
+        <v>0.1861</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.607</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1381</v>
+        <v>0.276</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2856</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>13.2278</v>
+        <v>15.2962</v>
       </c>
       <c r="E23" t="n">
         <v>19.9263</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.698600000000001</v>
+        <v>-4.630100000000001</v>
       </c>
       <c r="G23" t="n">
         <v>3.1738</v>
@@ -2239,7 +2239,7 @@
         <v>-6.590300000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>5.792299999999999</v>
+        <v>5.7923</v>
       </c>
       <c r="Q23" t="n">
         <v>-6.757899999999999</v>
@@ -2248,13 +2248,13 @@
         <v>12.5501</v>
       </c>
       <c r="S23" t="n">
-        <v>2.620299999999999</v>
+        <v>4.6886</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9631000000000001</v>
+        <v>0.9630000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>1.6573</v>
+        <v>3.7256</v>
       </c>
       <c r="V23" t="n">
         <v>1.6412</v>
